--- a/dataset_t6_grouped/results2/G4/G4_T3603_W0074F0003T0006Z000C1N19_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3603_W0074F0003T0006Z000C1N19_analysis.xlsx
@@ -480,10 +480,10 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>78.52855943263941</v>
+        <v>12.7608909078039</v>
       </c>
       <c r="D2" t="n">
-        <v>13.06063730885979</v>
+        <v>2.122353562689715</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
